--- a/specs/HTR_Specs_Tables.xlsx
+++ b/specs/HTR_Specs_Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\HTR_RaceCharts_Converter\specs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE8A0477-612C-436C-BB20-AD1F4BF8BB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ED86F80-06DA-45B5-B516-9B30241964F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="730" yWindow="1050" windowWidth="23440" windowHeight="14040" activeTab="2" xr2:uid="{2A7345D7-591B-4664-AD31-1007673BE600}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{2A7345D7-591B-4664-AD31-1007673BE600}"/>
   </bookViews>
   <sheets>
     <sheet name="Fields" sheetId="5" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="669">
   <si>
     <t>Text</t>
   </si>
@@ -2579,13 +2579,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.59999389629810485"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color theme="4" tint="0.59999389629810485"/>
@@ -2596,6 +2589,13 @@
         <top style="thin">
           <color theme="4" tint="0.59999389629810485"/>
         </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.59999389629810485"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
         <bottom style="thin">
           <color theme="4" tint="0.59999389629810485"/>
         </bottom>
@@ -2618,6 +2618,30 @@
           <color theme="4" tint="0.59999389629810485"/>
         </horizontal>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2800,30 +2824,6 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2874,12 +2874,12 @@
     <sortCondition ref="A1:A247"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12348EB0-2E05-4201-9D52-5E0CAFD48F75}" name="field" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{93DBB64E-EE33-43FD-8F3A-4A7EDA3057D8}" name="name" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{40E3FEA3-1544-43C4-B06F-597E40CAC8A8}" name="type" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{FFDFC4DB-0B6F-453C-88C1-8FA72023E314}" name="maxLength" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{797DB1CC-D4DC-4C71-8AFA-679F02E07E4D}" name="comments" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{49537A87-A9C8-4188-96E9-5130E1D65A96}" name="hasOptions" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{12348EB0-2E05-4201-9D52-5E0CAFD48F75}" name="field" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{93DBB64E-EE33-43FD-8F3A-4A7EDA3057D8}" name="name" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{40E3FEA3-1544-43C4-B06F-597E40CAC8A8}" name="type" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{FFDFC4DB-0B6F-453C-88C1-8FA72023E314}" name="maxLength" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{797DB1CC-D4DC-4C71-8AFA-679F02E07E4D}" name="comments" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{49537A87-A9C8-4188-96E9-5130E1D65A96}" name="hasOptions" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2889,8 +2889,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{76C8D9DA-B548-438D-B799-00D870652A9E}" name="lookup" displayName="lookup" ref="A1:C214" totalsRowShown="0">
   <autoFilter ref="A1:C214" xr:uid="{76C8D9DA-B548-438D-B799-00D870652A9E}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EA6F42D9-7DCE-4A14-9C9A-A7593C725658}" name="field" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{411E81CE-41B6-473A-B9FE-860425472405}" name="id" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{EA6F42D9-7DCE-4A14-9C9A-A7593C725658}" name="field" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{411E81CE-41B6-473A-B9FE-860425472405}" name="id" dataDxfId="14"/>
     <tableColumn id="3" xr3:uid="{CBE51C68-B69D-431E-A192-63B95A4C477D}" name="value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2898,22 +2898,22 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{B787B3A6-2CEE-4580-AFD7-41F639EDECDD}" name="RaceFractionalTimesbyDistance" displayName="RaceFractionalTimesbyDistance" ref="B3:G47" tableType="queryTable" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{B787B3A6-2CEE-4580-AFD7-41F639EDECDD}" name="RaceFractionalTimesbyDistance" displayName="RaceFractionalTimesbyDistance" ref="B3:G47" tableType="queryTable" totalsRowShown="0" headerRowDxfId="31" headerRowBorderDxfId="30" tableBorderDxfId="29" totalsRowBorderDxfId="28">
   <autoFilter ref="B3:G47" xr:uid="{B787B3A6-2CEE-4580-AFD7-41F639EDECDD}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{939F0159-4F9B-4057-9BC5-36D344F3B8AC}" uniqueName="1" name="distance" queryTableFieldId="1" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{81B499A8-0D93-47F1-A1B2-353B11C7EBFD}" uniqueName="2" name="f1" queryTableFieldId="2" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{B7879AD2-073F-4B6B-808A-2A96D7E39690}" uniqueName="3" name="f2" queryTableFieldId="3" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{505BCF72-3549-4ECE-82AC-D43412A35DC6}" uniqueName="4" name="f3" queryTableFieldId="4" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{83B3B0AA-6769-459F-B298-721B2BBB03F9}" uniqueName="5" name="f4" queryTableFieldId="5" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{0F80A3FC-7FBA-4E90-B532-78D8D4CD8CEF}" uniqueName="6" name="f5" queryTableFieldId="6" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{939F0159-4F9B-4057-9BC5-36D344F3B8AC}" uniqueName="1" name="distance" queryTableFieldId="1" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{81B499A8-0D93-47F1-A1B2-353B11C7EBFD}" uniqueName="2" name="f1" queryTableFieldId="2" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{B7879AD2-073F-4B6B-808A-2A96D7E39690}" uniqueName="3" name="f2" queryTableFieldId="3" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{505BCF72-3549-4ECE-82AC-D43412A35DC6}" uniqueName="4" name="f3" queryTableFieldId="4" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{83B3B0AA-6769-459F-B298-721B2BBB03F9}" uniqueName="5" name="f4" queryTableFieldId="5" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{0F80A3FC-7FBA-4E90-B532-78D8D4CD8CEF}" uniqueName="6" name="f5" queryTableFieldId="6" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{43EA538C-A70F-4D58-9DE1-930062C8AE1D}" name="PointsofCallinRacebyDistance" displayName="PointsofCallinRacebyDistance" ref="A2:F46" tableType="queryTable" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{43EA538C-A70F-4D58-9DE1-930062C8AE1D}" name="PointsofCallinRacebyDistance" displayName="PointsofCallinRacebyDistance" ref="A2:F46" tableType="queryTable" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="A2:F46" xr:uid="{43EA538C-A70F-4D58-9DE1-930062C8AE1D}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{05EEB0C5-140D-4ECF-9F88-0E72507177BD}" uniqueName="1" name="distance" queryTableFieldId="1" dataDxfId="9"/>
@@ -3388,6 +3388,9 @@
       <c r="E8" s="3" t="s">
         <v>90</v>
       </c>
+      <c r="F8" s="1" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
@@ -3422,6 +3425,9 @@
       <c r="E10" s="3" t="s">
         <v>92</v>
       </c>
+      <c r="F10" s="1" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="116" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
@@ -3439,6 +3445,9 @@
       <c r="E11" s="3" t="s">
         <v>93</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
@@ -3484,6 +3493,9 @@
       <c r="E14" s="3" t="s">
         <v>95</v>
       </c>
+      <c r="F14" s="1" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
@@ -3501,6 +3513,9 @@
       <c r="E15" s="3" t="s">
         <v>96</v>
       </c>
+      <c r="F15" s="1" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
@@ -3519,7 +3534,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -3533,7 +3548,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -3547,7 +3562,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -3561,7 +3576,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -3577,8 +3592,11 @@
       <c r="E20" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F20" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -3592,7 +3610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3606,7 +3624,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -3622,8 +3640,11 @@
       <c r="E23" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="F23" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -3639,8 +3660,11 @@
       <c r="E24" s="3" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F24" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -3657,7 +3681,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3671,7 +3695,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -3688,7 +3712,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3705,7 +3729,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3719,7 +3743,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -3733,7 +3757,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3747,7 +3771,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -3943,7 +3967,7 @@
         <v>Field 47</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -3952,7 +3976,7 @@
         <v>Field 48</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -3961,7 +3985,7 @@
         <v>Field 49</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -3970,7 +3994,7 @@
         <v>Field 50</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -3984,7 +4008,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -3995,7 +4019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -4012,7 +4036,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -4029,7 +4053,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="87" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -4045,8 +4069,11 @@
       <c r="E56" s="3" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F56" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -4057,7 +4084,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -4071,7 +4098,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -4085,7 +4112,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -4099,7 +4126,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -4116,7 +4143,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -4127,7 +4154,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -4138,7 +4165,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -4379,7 +4406,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -4393,7 +4420,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -4407,7 +4434,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -4421,7 +4448,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -4435,7 +4462,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -4449,7 +4476,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -4463,7 +4490,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -4477,7 +4504,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -4491,7 +4518,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -4505,7 +4532,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -4519,7 +4546,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -4532,8 +4559,11 @@
       <c r="E91" s="3" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F91" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -4547,7 +4577,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -4564,7 +4594,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -4578,7 +4608,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -4592,7 +4622,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -4606,7 +4636,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -4620,7 +4650,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -4637,7 +4667,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -4653,8 +4683,11 @@
       <c r="E99" s="3" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F99" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -4671,7 +4704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -4688,7 +4721,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -4699,7 +4732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -4713,7 +4746,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -4727,7 +4760,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -4741,7 +4774,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -4755,7 +4788,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -4769,7 +4802,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -4786,7 +4819,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -4803,7 +4836,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -4817,7 +4850,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -4831,7 +4864,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -4848,7 +4881,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -4864,8 +4897,11 @@
       <c r="E113" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F113" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -4879,7 +4915,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -4896,7 +4932,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -4910,7 +4946,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -4924,7 +4960,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -4933,7 +4969,7 @@
         <v>Field 117</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -4942,7 +4978,7 @@
         <v>Field 118</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -4951,7 +4987,7 @@
         <v>Field 119</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -4960,7 +4996,7 @@
         <v>Field 120</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -4969,7 +5005,7 @@
         <v>Field 121</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -4978,7 +5014,7 @@
         <v>Field 122</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -4987,7 +5023,7 @@
         <v>Field 123</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -4996,7 +5032,7 @@
         <v>Field 124</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -5005,7 +5041,7 @@
         <v>Field 125</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -5014,7 +5050,7 @@
         <v>Field 126</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -5023,7 +5059,7 @@
         <v>Field 127</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -5032,7 +5068,7 @@
         <v>Field 128</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -5041,7 +5077,7 @@
         <v>Field 129</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -5050,7 +5086,7 @@
         <v>Field 130</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="203" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" ht="203" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -5066,8 +5102,11 @@
       <c r="E132" s="3" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F132" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -5081,7 +5120,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -5095,7 +5134,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -5109,7 +5148,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -5126,7 +5165,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -5140,7 +5179,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -5154,7 +5193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -5165,7 +5204,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -5176,7 +5215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -5187,7 +5226,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -5201,7 +5240,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -5212,7 +5251,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>143</v>
       </c>

--- a/specs/HTR_Specs_Tables.xlsx
+++ b/specs/HTR_Specs_Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\HTR_RaceCharts_Converter\specs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ED86F80-06DA-45B5-B516-9B30241964F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4533B251-4197-4DB1-A1DF-8D157EEC58A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{2A7345D7-591B-4664-AD31-1007673BE600}"/>
+    <workbookView xWindow="1780" yWindow="2380" windowWidth="23440" windowHeight="14040" activeTab="1" xr2:uid="{2A7345D7-591B-4664-AD31-1007673BE600}"/>
   </bookViews>
   <sheets>
     <sheet name="Fields" sheetId="5" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="677">
   <si>
     <t>Text</t>
   </si>
@@ -1679,15 +1679,6 @@
     <t>No shoes</t>
   </si>
   <si>
-    <t>Apprentice Type 1</t>
-  </si>
-  <si>
-    <t>Apprentice Type 2</t>
-  </si>
-  <si>
-    <t>Apprentice Type 3</t>
-  </si>
-  <si>
     <t>J</t>
   </si>
   <si>
@@ -2064,6 +2055,39 @@
   </si>
   <si>
     <t>call5</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Apprentice Type 1 (5 lbs)</t>
+  </si>
+  <si>
+    <t>Apprentice Type 2 (7 lbs)</t>
+  </si>
+  <si>
+    <t>Apprentice Type 3 (10 lbs)</t>
   </si>
 </sst>
 </file>
@@ -2363,7 +2387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2400,6 +2424,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2620,30 +2647,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -2824,6 +2827,30 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2874,23 +2901,23 @@
     <sortCondition ref="A1:A247"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12348EB0-2E05-4201-9D52-5E0CAFD48F75}" name="field" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{93DBB64E-EE33-43FD-8F3A-4A7EDA3057D8}" name="name" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{40E3FEA3-1544-43C4-B06F-597E40CAC8A8}" name="type" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{FFDFC4DB-0B6F-453C-88C1-8FA72023E314}" name="maxLength" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{797DB1CC-D4DC-4C71-8AFA-679F02E07E4D}" name="comments" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{49537A87-A9C8-4188-96E9-5130E1D65A96}" name="hasOptions" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{12348EB0-2E05-4201-9D52-5E0CAFD48F75}" name="field" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{93DBB64E-EE33-43FD-8F3A-4A7EDA3057D8}" name="name" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{40E3FEA3-1544-43C4-B06F-597E40CAC8A8}" name="type" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{FFDFC4DB-0B6F-453C-88C1-8FA72023E314}" name="maxLength" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{797DB1CC-D4DC-4C71-8AFA-679F02E07E4D}" name="comments" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{49537A87-A9C8-4188-96E9-5130E1D65A96}" name="hasOptions" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{76C8D9DA-B548-438D-B799-00D870652A9E}" name="lookup" displayName="lookup" ref="A1:C214" totalsRowShown="0">
-  <autoFilter ref="A1:C214" xr:uid="{76C8D9DA-B548-438D-B799-00D870652A9E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{76C8D9DA-B548-438D-B799-00D870652A9E}" name="lookup" displayName="lookup" ref="A1:C217" totalsRowShown="0">
+  <autoFilter ref="A1:C217" xr:uid="{76C8D9DA-B548-438D-B799-00D870652A9E}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EA6F42D9-7DCE-4A14-9C9A-A7593C725658}" name="field" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{411E81CE-41B6-473A-B9FE-860425472405}" name="id" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{EA6F42D9-7DCE-4A14-9C9A-A7593C725658}" name="field" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{411E81CE-41B6-473A-B9FE-860425472405}" name="id" dataDxfId="24"/>
     <tableColumn id="3" xr3:uid="{CBE51C68-B69D-431E-A192-63B95A4C477D}" name="value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2898,15 +2925,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{B787B3A6-2CEE-4580-AFD7-41F639EDECDD}" name="RaceFractionalTimesbyDistance" displayName="RaceFractionalTimesbyDistance" ref="B3:G47" tableType="queryTable" totalsRowShown="0" headerRowDxfId="31" headerRowBorderDxfId="30" tableBorderDxfId="29" totalsRowBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{B787B3A6-2CEE-4580-AFD7-41F639EDECDD}" name="RaceFractionalTimesbyDistance" displayName="RaceFractionalTimesbyDistance" ref="B3:G47" tableType="queryTable" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <autoFilter ref="B3:G47" xr:uid="{B787B3A6-2CEE-4580-AFD7-41F639EDECDD}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{939F0159-4F9B-4057-9BC5-36D344F3B8AC}" uniqueName="1" name="distance" queryTableFieldId="1" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{81B499A8-0D93-47F1-A1B2-353B11C7EBFD}" uniqueName="2" name="f1" queryTableFieldId="2" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{B7879AD2-073F-4B6B-808A-2A96D7E39690}" uniqueName="3" name="f2" queryTableFieldId="3" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{505BCF72-3549-4ECE-82AC-D43412A35DC6}" uniqueName="4" name="f3" queryTableFieldId="4" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{83B3B0AA-6769-459F-B298-721B2BBB03F9}" uniqueName="5" name="f4" queryTableFieldId="5" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{0F80A3FC-7FBA-4E90-B532-78D8D4CD8CEF}" uniqueName="6" name="f5" queryTableFieldId="6" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{939F0159-4F9B-4057-9BC5-36D344F3B8AC}" uniqueName="1" name="distance" queryTableFieldId="1" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{81B499A8-0D93-47F1-A1B2-353B11C7EBFD}" uniqueName="2" name="f1" queryTableFieldId="2" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{B7879AD2-073F-4B6B-808A-2A96D7E39690}" uniqueName="3" name="f2" queryTableFieldId="3" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{505BCF72-3549-4ECE-82AC-D43412A35DC6}" uniqueName="4" name="f3" queryTableFieldId="4" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{83B3B0AA-6769-459F-B298-721B2BBB03F9}" uniqueName="5" name="f4" queryTableFieldId="5" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{0F80A3FC-7FBA-4E90-B532-78D8D4CD8CEF}" uniqueName="6" name="f5" queryTableFieldId="6" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3257,22 +3284,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>652</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>655</v>
       </c>
       <c r="G1" s="4"/>
     </row>
@@ -6504,7 +6531,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58DC5A85-7B0A-4725-A0BE-69CD267E14C8}">
-  <dimension ref="A1:C214"/>
+  <dimension ref="A1:C217"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="1" customWidth="1"/>
@@ -6514,13 +6541,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C1" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -7011,8 +7038,8 @@
       <c r="A46" s="1">
         <v>14</v>
       </c>
-      <c r="B46" s="1">
-        <v>2</v>
+      <c r="B46" s="26" t="s">
+        <v>666</v>
       </c>
       <c r="C46" t="s">
         <v>459</v>
@@ -7022,8 +7049,8 @@
       <c r="A47" s="1">
         <v>14</v>
       </c>
-      <c r="B47" s="1">
-        <v>3</v>
+      <c r="B47" s="26" t="s">
+        <v>667</v>
       </c>
       <c r="C47" t="s">
         <v>460</v>
@@ -7033,8 +7060,8 @@
       <c r="A48" s="1">
         <v>14</v>
       </c>
-      <c r="B48" s="1">
-        <v>4</v>
+      <c r="B48" s="26" t="s">
+        <v>668</v>
       </c>
       <c r="C48" t="s">
         <v>461</v>
@@ -7044,8 +7071,8 @@
       <c r="A49" s="1">
         <v>14</v>
       </c>
-      <c r="B49" s="1">
-        <v>5</v>
+      <c r="B49" s="26" t="s">
+        <v>669</v>
       </c>
       <c r="C49" t="s">
         <v>462</v>
@@ -7055,8 +7082,8 @@
       <c r="A50" s="1">
         <v>14</v>
       </c>
-      <c r="B50" s="1">
-        <v>6</v>
+      <c r="B50" s="26" t="s">
+        <v>670</v>
       </c>
       <c r="C50" t="s">
         <v>463</v>
@@ -7066,8 +7093,8 @@
       <c r="A51" s="1">
         <v>14</v>
       </c>
-      <c r="B51" s="1">
-        <v>7</v>
+      <c r="B51" s="26" t="s">
+        <v>671</v>
       </c>
       <c r="C51" t="s">
         <v>464</v>
@@ -7077,8 +7104,8 @@
       <c r="A52" s="1">
         <v>14</v>
       </c>
-      <c r="B52" s="1">
-        <v>8</v>
+      <c r="B52" s="26" t="s">
+        <v>672</v>
       </c>
       <c r="C52" t="s">
         <v>465</v>
@@ -7088,8 +7115,8 @@
       <c r="A53" s="1">
         <v>14</v>
       </c>
-      <c r="B53" s="1">
-        <v>9</v>
+      <c r="B53" s="26" t="s">
+        <v>673</v>
       </c>
       <c r="C53" t="s">
         <v>466</v>
@@ -7939,18 +7966,18 @@
         <v>405</v>
       </c>
       <c r="C130" t="s">
-        <v>540</v>
+        <v>674</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>90</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>406</v>
+      <c r="B131" s="6">
+        <v>5</v>
       </c>
       <c r="C131" t="s">
-        <v>541</v>
+        <v>674</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.35">
@@ -7958,43 +7985,43 @@
         <v>90</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C132" t="s">
-        <v>542</v>
+        <v>675</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
-        <v>98</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>361</v>
+        <v>90</v>
+      </c>
+      <c r="B133" s="1">
+        <v>7</v>
       </c>
       <c r="C133" t="s">
-        <v>409</v>
+        <v>675</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>271</v>
+        <v>407</v>
       </c>
       <c r="C134" t="s">
-        <v>410</v>
+        <v>676</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
-        <v>98</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>272</v>
+        <v>90</v>
+      </c>
+      <c r="B135" s="1">
+        <v>10</v>
       </c>
       <c r="C135" t="s">
-        <v>411</v>
+        <v>676</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.35">
@@ -8002,10 +8029,10 @@
         <v>98</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>28</v>
+        <v>361</v>
       </c>
       <c r="C136" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.35">
@@ -8013,10 +8040,10 @@
         <v>98</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>543</v>
+        <v>271</v>
       </c>
       <c r="C137" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.35">
@@ -8024,10 +8051,10 @@
         <v>98</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>544</v>
+        <v>272</v>
       </c>
       <c r="C138" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
@@ -8035,10 +8062,10 @@
         <v>98</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>273</v>
+        <v>28</v>
       </c>
       <c r="C139" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
@@ -8046,10 +8073,10 @@
         <v>98</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>26</v>
+        <v>540</v>
       </c>
       <c r="C140" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
@@ -8057,10 +8084,10 @@
         <v>98</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C141" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
@@ -8068,10 +8095,10 @@
         <v>98</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>30</v>
+        <v>273</v>
       </c>
       <c r="C142" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
@@ -8079,10 +8106,10 @@
         <v>98</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C143" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.35">
@@ -8090,10 +8117,10 @@
         <v>98</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>277</v>
+        <v>542</v>
       </c>
       <c r="C144" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.35">
@@ -8101,10 +8128,10 @@
         <v>98</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C145" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.35">
@@ -8112,10 +8139,10 @@
         <v>98</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C146" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.35">
@@ -8123,10 +8150,10 @@
         <v>98</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>546</v>
+        <v>277</v>
       </c>
       <c r="C147" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.35">
@@ -8134,10 +8161,10 @@
         <v>98</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>276</v>
+        <v>33</v>
       </c>
       <c r="C148" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.35">
@@ -8145,10 +8172,10 @@
         <v>98</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="C149" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.35">
@@ -8156,10 +8183,10 @@
         <v>98</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>270</v>
+        <v>543</v>
       </c>
       <c r="C150" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.35">
@@ -8167,43 +8194,43 @@
         <v>98</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>404</v>
+        <v>276</v>
       </c>
       <c r="C151" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>361</v>
+        <v>268</v>
       </c>
       <c r="C152" t="s">
-        <v>547</v>
+        <v>424</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>18</v>
+        <v>270</v>
       </c>
       <c r="C153" t="s">
-        <v>548</v>
+        <v>425</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>30</v>
+        <v>404</v>
       </c>
       <c r="C154" t="s">
-        <v>549</v>
+        <v>426</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
@@ -8211,10 +8238,10 @@
         <v>112</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>22</v>
+        <v>361</v>
       </c>
       <c r="C155" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.35">
@@ -8222,54 +8249,54 @@
         <v>112</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>276</v>
+        <v>18</v>
       </c>
       <c r="C156" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>552</v>
+        <v>30</v>
       </c>
       <c r="C157" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
-        <v>131</v>
-      </c>
-      <c r="B158" s="1">
-        <v>0</v>
+        <v>112</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C158" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
-        <v>131</v>
-      </c>
-      <c r="B159" s="1">
-        <v>1</v>
+        <v>112</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="C159" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>131</v>
       </c>
-      <c r="B160" s="1">
-        <v>13</v>
+      <c r="B160" s="1" t="s">
+        <v>549</v>
       </c>
       <c r="C160" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
@@ -8277,10 +8304,10 @@
         <v>131</v>
       </c>
       <c r="B161" s="1">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C161" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
@@ -8288,10 +8315,10 @@
         <v>131</v>
       </c>
       <c r="B162" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C162" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.35">
@@ -8299,10 +8326,10 @@
         <v>131</v>
       </c>
       <c r="B163" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C163" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
@@ -8310,21 +8337,21 @@
         <v>131</v>
       </c>
       <c r="B164" s="1">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C164" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>131</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>561</v>
+      <c r="B165" s="1">
+        <v>2</v>
       </c>
       <c r="C165" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.35">
@@ -8332,76 +8359,76 @@
         <v>131</v>
       </c>
       <c r="B166" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C166" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>131</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>564</v>
+      <c r="B167" s="1">
+        <v>4</v>
       </c>
       <c r="C167" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>131</v>
       </c>
-      <c r="B168" s="1">
-        <v>6</v>
+      <c r="B168" s="1" t="s">
+        <v>558</v>
       </c>
       <c r="C168" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>131</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>567</v>
+      <c r="B169" s="1">
+        <v>5</v>
       </c>
       <c r="C169" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>131</v>
       </c>
-      <c r="B170" s="1">
-        <v>7</v>
+      <c r="B170" s="1" t="s">
+        <v>561</v>
       </c>
       <c r="C170" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>131</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>570</v>
+      <c r="B171" s="1">
+        <v>6</v>
       </c>
       <c r="C171" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>131</v>
       </c>
-      <c r="B172" s="1">
-        <v>8</v>
+      <c r="B172" s="1" t="s">
+        <v>564</v>
       </c>
       <c r="C172" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.35">
@@ -8409,10 +8436,10 @@
         <v>131</v>
       </c>
       <c r="B173" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C173" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.35">
@@ -8420,32 +8447,32 @@
         <v>131</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="C174" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>131</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>361</v>
+      <c r="B175" s="1">
+        <v>8</v>
       </c>
       <c r="C175" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>131</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>274</v>
+      <c r="B176" s="1">
+        <v>9</v>
       </c>
       <c r="C176" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.35">
@@ -8453,10 +8480,10 @@
         <v>131</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="C177" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.35">
@@ -8464,10 +8491,10 @@
         <v>131</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>269</v>
+        <v>361</v>
       </c>
       <c r="C178" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.35">
@@ -8475,10 +8502,10 @@
         <v>131</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>18</v>
+        <v>274</v>
       </c>
       <c r="C179" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.35">
@@ -8486,10 +8513,10 @@
         <v>131</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>271</v>
+        <v>575</v>
       </c>
       <c r="C180" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.35">
@@ -8497,10 +8524,10 @@
         <v>131</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C181" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.35">
@@ -8508,10 +8535,10 @@
         <v>131</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>272</v>
+        <v>18</v>
       </c>
       <c r="C182" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.35">
@@ -8519,10 +8546,10 @@
         <v>131</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>31</v>
+        <v>271</v>
       </c>
       <c r="C183" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.35">
@@ -8530,10 +8557,10 @@
         <v>131</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>586</v>
+        <v>278</v>
       </c>
       <c r="C184" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.35">
@@ -8541,10 +8568,10 @@
         <v>131</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>588</v>
+        <v>272</v>
       </c>
       <c r="C185" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.35">
@@ -8552,10 +8579,10 @@
         <v>131</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C186" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.35">
@@ -8563,10 +8590,10 @@
         <v>131</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="C187" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.35">
@@ -8574,10 +8601,10 @@
         <v>131</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>543</v>
+        <v>585</v>
       </c>
       <c r="C188" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.35">
@@ -8585,10 +8612,10 @@
         <v>131</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>544</v>
+        <v>28</v>
       </c>
       <c r="C189" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.35">
@@ -8596,10 +8623,10 @@
         <v>131</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>273</v>
+        <v>588</v>
       </c>
       <c r="C190" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.35">
@@ -8607,10 +8634,10 @@
         <v>131</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>596</v>
+        <v>540</v>
       </c>
       <c r="C191" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.35">
@@ -8618,10 +8645,10 @@
         <v>131</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>26</v>
+        <v>541</v>
       </c>
       <c r="C192" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.35">
@@ -8629,10 +8656,10 @@
         <v>131</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>545</v>
+        <v>273</v>
       </c>
       <c r="C193" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.35">
@@ -8640,10 +8667,10 @@
         <v>131</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>30</v>
+        <v>593</v>
       </c>
       <c r="C194" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.35">
@@ -8651,10 +8678,10 @@
         <v>131</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>601</v>
+        <v>26</v>
       </c>
       <c r="C195" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.35">
@@ -8662,10 +8689,10 @@
         <v>131</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>22</v>
+        <v>542</v>
       </c>
       <c r="C196" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.35">
@@ -8673,10 +8700,10 @@
         <v>131</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>604</v>
+        <v>30</v>
       </c>
       <c r="C197" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.35">
@@ -8684,10 +8711,10 @@
         <v>131</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="C198" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.35">
@@ -8695,10 +8722,10 @@
         <v>131</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>608</v>
+        <v>22</v>
       </c>
       <c r="C199" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.35">
@@ -8706,10 +8733,10 @@
         <v>131</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="C200" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.35">
@@ -8717,10 +8744,10 @@
         <v>131</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>275</v>
+        <v>603</v>
       </c>
       <c r="C201" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.35">
@@ -8728,10 +8755,10 @@
         <v>131</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>277</v>
+        <v>605</v>
       </c>
       <c r="C202" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.35">
@@ -8739,10 +8766,10 @@
         <v>131</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>33</v>
+        <v>607</v>
       </c>
       <c r="C203" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.35">
@@ -8750,10 +8777,10 @@
         <v>131</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>615</v>
+        <v>275</v>
       </c>
       <c r="C204" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.35">
@@ -8761,10 +8788,10 @@
         <v>131</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>617</v>
+        <v>277</v>
       </c>
       <c r="C205" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.35">
@@ -8772,10 +8799,10 @@
         <v>131</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C206" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.35">
@@ -8783,10 +8810,10 @@
         <v>131</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>546</v>
+        <v>612</v>
       </c>
       <c r="C207" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.35">
@@ -8794,10 +8821,10 @@
         <v>131</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>276</v>
+        <v>614</v>
       </c>
       <c r="C208" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.35">
@@ -8805,10 +8832,10 @@
         <v>131</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>622</v>
+        <v>20</v>
       </c>
       <c r="C209" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.35">
@@ -8816,10 +8843,10 @@
         <v>131</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>279</v>
+        <v>543</v>
       </c>
       <c r="C210" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.35">
@@ -8827,10 +8854,10 @@
         <v>131</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>625</v>
+        <v>276</v>
       </c>
       <c r="C211" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.35">
@@ -8838,10 +8865,10 @@
         <v>131</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>268</v>
+        <v>619</v>
       </c>
       <c r="C212" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.35">
@@ -8849,10 +8876,10 @@
         <v>131</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="C213" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.35">
@@ -8860,10 +8887,43 @@
         <v>131</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="C214" t="s">
-        <v>630</v>
+        <v>623</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A215" s="1">
+        <v>131</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C215" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A216" s="1">
+        <v>131</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C216" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217" s="1">
+        <v>131</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="C217" t="s">
+        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -8893,7 +8953,7 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B2" s="25" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
@@ -8903,22 +8963,22 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>658</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>659</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>660</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>661</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>662</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.35">
@@ -8926,19 +8986,19 @@
         <v>2</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.35">
@@ -8946,19 +9006,19 @@
         <v>2.5</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.35">
@@ -8966,19 +9026,19 @@
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.35">
@@ -8986,19 +9046,19 @@
         <v>3.5</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.35">
@@ -9006,19 +9066,19 @@
         <v>3.75</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.35">
@@ -9026,19 +9086,19 @@
         <v>4</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.35">
@@ -9046,19 +9106,19 @@
         <v>4.5</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.35">
@@ -9066,19 +9126,19 @@
         <v>5</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.35">
@@ -9086,19 +9146,19 @@
         <v>5.25</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.35">
@@ -9106,19 +9166,19 @@
         <v>5.5</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.35">
@@ -9126,19 +9186,19 @@
         <v>6</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.35">
@@ -9146,19 +9206,19 @@
         <v>6.5</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F15" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.35">
@@ -9166,19 +9226,19 @@
         <v>7</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F16" s="11" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.35">
@@ -9186,19 +9246,19 @@
         <v>7.5</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="F17" s="11" t="s">
         <v>644</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>646</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>647</v>
-      </c>
       <c r="G17" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.35">
@@ -9206,19 +9266,19 @@
         <v>8</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="F18" s="11" t="s">
         <v>644</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>646</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>647</v>
-      </c>
       <c r="G18" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.35">
@@ -9226,19 +9286,19 @@
         <v>8.18</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F19" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.35">
@@ -9246,19 +9306,19 @@
         <v>8.32</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F20" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.35">
@@ -9266,19 +9326,19 @@
         <v>8.5</v>
       </c>
       <c r="C21" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F21" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.35">
@@ -9286,19 +9346,19 @@
         <v>9</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F22" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.35">
@@ -9306,19 +9366,19 @@
         <v>9.5</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D23" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F23" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.35">
@@ -9326,19 +9386,19 @@
         <v>10</v>
       </c>
       <c r="C24" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F24" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.35">
@@ -9346,19 +9406,19 @@
         <v>10.5</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D25" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F25" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.35">
@@ -9366,19 +9426,19 @@
         <v>11</v>
       </c>
       <c r="C26" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E26" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D26" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F26" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.35">
@@ -9386,19 +9446,19 @@
         <v>11.5</v>
       </c>
       <c r="C27" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F27" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.35">
@@ -9406,19 +9466,19 @@
         <v>12</v>
       </c>
       <c r="C28" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E28" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F28" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.35">
@@ -9426,19 +9486,19 @@
         <v>12.5</v>
       </c>
       <c r="C29" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E29" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F29" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.35">
@@ -9446,19 +9506,19 @@
         <v>13</v>
       </c>
       <c r="C30" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D30" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F30" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.35">
@@ -9466,19 +9526,19 @@
         <v>13.5</v>
       </c>
       <c r="C31" s="11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>643</v>
       </c>
-      <c r="D31" s="11" t="s">
-        <v>644</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>646</v>
-      </c>
       <c r="F31" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.35">
@@ -9486,19 +9546,19 @@
         <v>14</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.35">
@@ -9506,19 +9566,19 @@
         <v>14.5</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.35">
@@ -9526,19 +9586,19 @@
         <v>15</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D34" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="G34" s="12" t="s">
         <v>632</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.35">
@@ -9546,19 +9606,19 @@
         <v>15.5</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D35" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="G35" s="12" t="s">
         <v>632</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.35">
@@ -9566,19 +9626,19 @@
         <v>16</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D36" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="G36" s="12" t="s">
         <v>632</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="G36" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.35">
@@ -9586,19 +9646,19 @@
         <v>16.18</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D37" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="G37" s="12" t="s">
         <v>632</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.35">
@@ -9606,19 +9666,19 @@
         <v>16.32</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D38" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="G38" s="12" t="s">
         <v>632</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.35">
@@ -9626,19 +9686,19 @@
         <v>16.5</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D39" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="G39" s="12" t="s">
         <v>632</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.35">
@@ -9646,19 +9706,19 @@
         <v>17</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D40" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="G40" s="12" t="s">
         <v>632</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.35">
@@ -9666,19 +9726,19 @@
         <v>17.5</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D41" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="G41" s="12" t="s">
         <v>632</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.35">
@@ -9686,19 +9746,19 @@
         <v>18</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D42" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="G42" s="12" t="s">
         <v>632</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.35">
@@ -9706,19 +9766,19 @@
         <v>18.5</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D43" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="G43" s="12" t="s">
         <v>632</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.35">
@@ -9726,19 +9786,19 @@
         <v>19</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D44" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="G44" s="12" t="s">
         <v>632</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.35">
@@ -9746,19 +9806,19 @@
         <v>20</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D45" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="G45" s="12" t="s">
         <v>632</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.35">
@@ -9766,19 +9826,19 @@
         <v>21</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D46" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>630</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="G46" s="12" t="s">
         <v>632</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>634</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.35">
@@ -9786,19 +9846,19 @@
         <v>22</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D47" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>630</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="G47" s="15" t="s">
         <v>632</v>
-      </c>
-      <c r="E47" s="14" t="s">
-        <v>633</v>
-      </c>
-      <c r="F47" s="14" t="s">
-        <v>634</v>
-      </c>
-      <c r="G47" s="15" t="s">
-        <v>635</v>
       </c>
     </row>
   </sheetData>
@@ -9819,7 +9879,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -9829,22 +9889,22 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>661</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>662</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>664</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>665</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>666</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>667</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -9852,19 +9912,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -9872,19 +9932,19 @@
         <v>2.5</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -9892,19 +9952,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -9912,19 +9972,19 @@
         <v>3.5</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -9932,19 +9992,19 @@
         <v>3.75</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -9952,19 +10012,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -9972,19 +10032,19 @@
         <v>4.5</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -9992,19 +10052,19 @@
         <v>5</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -10012,19 +10072,19 @@
         <v>5.25</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -10032,19 +10092,19 @@
         <v>5.5</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -10052,19 +10112,19 @@
         <v>6</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -10072,19 +10132,19 @@
         <v>6.5</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -10092,19 +10152,19 @@
         <v>7</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -10112,19 +10172,19 @@
         <v>7.5</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -10132,19 +10192,19 @@
         <v>8</v>
       </c>
       <c r="B17" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="D17" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="C17" s="20" t="s">
-        <v>644</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>646</v>
-      </c>
       <c r="E17" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -10152,19 +10212,19 @@
         <v>8.18</v>
       </c>
       <c r="B18" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="D18" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="C18" s="20" t="s">
-        <v>644</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>646</v>
-      </c>
       <c r="E18" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -10172,19 +10232,19 @@
         <v>8.32</v>
       </c>
       <c r="B19" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="D19" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="C19" s="20" t="s">
-        <v>644</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>646</v>
-      </c>
       <c r="E19" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -10192,19 +10252,19 @@
         <v>8.5</v>
       </c>
       <c r="B20" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="C20" s="20" t="s">
-        <v>644</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>646</v>
-      </c>
       <c r="E20" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -10212,19 +10272,19 @@
         <v>9</v>
       </c>
       <c r="B21" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="D21" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>644</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>646</v>
-      </c>
       <c r="E21" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -10232,19 +10292,19 @@
         <v>9.5</v>
       </c>
       <c r="B22" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="D22" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="C22" s="20" t="s">
-        <v>644</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>646</v>
-      </c>
       <c r="E22" s="20" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -10252,19 +10312,19 @@
         <v>10</v>
       </c>
       <c r="B23" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="D23" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>644</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>646</v>
-      </c>
       <c r="E23" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -10272,19 +10332,19 @@
         <v>10.5</v>
       </c>
       <c r="B24" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="D24" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>644</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>646</v>
-      </c>
       <c r="E24" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -10292,19 +10352,19 @@
         <v>11</v>
       </c>
       <c r="B25" s="20" t="s">
+        <v>640</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>641</v>
+      </c>
+      <c r="D25" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>644</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>646</v>
-      </c>
       <c r="E25" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -10312,19 +10372,19 @@
         <v>11.5</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E26" s="20" t="s">
+        <v>630</v>
+      </c>
+      <c r="F26" s="21" t="s">
         <v>633</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -10332,19 +10392,19 @@
         <v>12</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E27" s="20" t="s">
+        <v>630</v>
+      </c>
+      <c r="F27" s="21" t="s">
         <v>633</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -10352,19 +10412,19 @@
         <v>12.5</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E28" s="20" t="s">
+        <v>630</v>
+      </c>
+      <c r="F28" s="21" t="s">
         <v>633</v>
-      </c>
-      <c r="F28" s="21" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -10372,19 +10432,19 @@
         <v>13</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -10392,19 +10452,19 @@
         <v>13.5</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D30" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -10412,19 +10472,19 @@
         <v>14</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D31" s="20" t="s">
+        <v>630</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="F31" s="21" t="s">
         <v>633</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -10432,19 +10492,19 @@
         <v>14.5</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D32" s="20" t="s">
+        <v>630</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="F32" s="21" t="s">
         <v>633</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -10452,19 +10512,19 @@
         <v>15</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -10472,19 +10532,19 @@
         <v>15.5</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D34" s="20" t="s">
+        <v>630</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>635</v>
+      </c>
+      <c r="F34" s="21" t="s">
         <v>633</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>638</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -10492,19 +10552,19 @@
         <v>16</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C35" s="20" t="s">
+        <v>629</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="E35" s="20" t="s">
         <v>632</v>
       </c>
-      <c r="D35" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="E35" s="20" t="s">
-        <v>635</v>
-      </c>
       <c r="F35" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -10512,19 +10572,19 @@
         <v>16.18</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C36" s="20" t="s">
+        <v>629</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="E36" s="20" t="s">
         <v>632</v>
       </c>
-      <c r="D36" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>635</v>
-      </c>
       <c r="F36" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -10532,19 +10592,19 @@
         <v>16.32</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C37" s="20" t="s">
+        <v>629</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="E37" s="20" t="s">
         <v>632</v>
       </c>
-      <c r="D37" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>635</v>
-      </c>
       <c r="F37" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -10552,19 +10612,19 @@
         <v>16.5</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C38" s="20" t="s">
+        <v>629</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="E38" s="20" t="s">
         <v>632</v>
       </c>
-      <c r="D38" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>635</v>
-      </c>
       <c r="F38" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -10572,19 +10632,19 @@
         <v>17</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C39" s="20" t="s">
+        <v>629</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="E39" s="20" t="s">
         <v>632</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>635</v>
-      </c>
       <c r="F39" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -10592,19 +10652,19 @@
         <v>17.5</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C40" s="20" t="s">
+        <v>629</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>631</v>
+      </c>
+      <c r="E40" s="20" t="s">
         <v>632</v>
       </c>
-      <c r="D40" s="20" t="s">
-        <v>634</v>
-      </c>
-      <c r="E40" s="20" t="s">
-        <v>635</v>
-      </c>
       <c r="F40" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -10612,19 +10672,19 @@
         <v>18</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -10632,19 +10692,19 @@
         <v>18.5</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -10652,19 +10712,19 @@
         <v>19</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -10672,19 +10732,19 @@
         <v>20</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -10692,19 +10752,19 @@
         <v>21</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -10712,19 +10772,19 @@
         <v>22</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="F46" s="24" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>

--- a/specs/HTR_Specs_Tables.xlsx
+++ b/specs/HTR_Specs_Tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\HTR_RaceCharts_Converter\specs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E309936C-4389-496D-8B14-6E8A0FC3B564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFE6E64-69BC-47F4-8921-1E657852850A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{2A7345D7-591B-4664-AD31-1007673BE600}"/>
   </bookViews>
@@ -2510,12 +2510,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -2881,6 +2875,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2926,10 +2926,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="3" xr16:uid="{BBA323B1-E1FB-42DE-84DF-289F2AF9E88E}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="7">
@@ -2967,12 +2963,12 @@
     <sortCondition ref="A1:A245"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12348EB0-2E05-4201-9D52-5E0CAFD48F75}" name="field" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{93DBB64E-EE33-43FD-8F3A-4A7EDA3057D8}" name="name" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{40E3FEA3-1544-43C4-B06F-597E40CAC8A8}" name="type" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{FFDFC4DB-0B6F-453C-88C1-8FA72023E314}" name="maxLength" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{797DB1CC-D4DC-4C71-8AFA-679F02E07E4D}" name="comments" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{49537A87-A9C8-4188-96E9-5130E1D65A96}" name="hasOptions" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{12348EB0-2E05-4201-9D52-5E0CAFD48F75}" name="field" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{93DBB64E-EE33-43FD-8F3A-4A7EDA3057D8}" name="name" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{40E3FEA3-1544-43C4-B06F-597E40CAC8A8}" name="type" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{FFDFC4DB-0B6F-453C-88C1-8FA72023E314}" name="maxLength" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{797DB1CC-D4DC-4C71-8AFA-679F02E07E4D}" name="comments" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{49537A87-A9C8-4188-96E9-5130E1D65A96}" name="hasOptions" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2985,12 +2981,12 @@
     <sortCondition ref="A1:A245"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{56B31709-7838-423E-B8D6-E0B832D87CA1}" name="field" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{7BD91985-B1F5-4292-8CF0-DA31B9020F62}" name="name" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{6141D3E1-D887-4122-AA6B-CC1755E083A4}" name="type" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{E8E92D6D-1D02-4E12-B636-880AAA119407}" name="maxLength" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{22CD5A51-81C5-4EBE-A2D1-F40F2EC1E540}" name="comments" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{BD5FB8BE-E6BF-43F9-AE80-9FC6D8ABE408}" name="hasOptions" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{56B31709-7838-423E-B8D6-E0B832D87CA1}" name="field" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{7BD91985-B1F5-4292-8CF0-DA31B9020F62}" name="name" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{6141D3E1-D887-4122-AA6B-CC1755E083A4}" name="type" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{E8E92D6D-1D02-4E12-B636-880AAA119407}" name="maxLength" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{22CD5A51-81C5-4EBE-A2D1-F40F2EC1E540}" name="comments" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{BD5FB8BE-E6BF-43F9-AE80-9FC6D8ABE408}" name="hasOptions" dataDxfId="30"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3000,8 +2996,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{76C8D9DA-B548-438D-B799-00D870652A9E}" name="lookup" displayName="lookup" ref="A1:C1261" totalsRowShown="0">
   <autoFilter ref="A1:C1261" xr:uid="{76C8D9DA-B548-438D-B799-00D870652A9E}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EA6F42D9-7DCE-4A14-9C9A-A7593C725658}" name="field" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{411E81CE-41B6-473A-B9FE-860425472405}" name="id" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{EA6F42D9-7DCE-4A14-9C9A-A7593C725658}" name="field" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{411E81CE-41B6-473A-B9FE-860425472405}" name="id" dataDxfId="28"/>
     <tableColumn id="3" xr3:uid="{CBE51C68-B69D-431E-A192-63B95A4C477D}" name="value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3009,30 +3005,30 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{B787B3A6-2CEE-4580-AFD7-41F639EDECDD}" name="RaceFractionalTimesbyDistance" displayName="RaceFractionalTimesbyDistance" ref="B3:G47" tableType="queryTable" totalsRowShown="0" headerRowDxfId="29" headerRowBorderDxfId="28" tableBorderDxfId="27" totalsRowBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{B787B3A6-2CEE-4580-AFD7-41F639EDECDD}" name="RaceFractionalTimesbyDistance" displayName="RaceFractionalTimesbyDistance" ref="B3:G47" tableType="queryTable" totalsRowShown="0" headerRowDxfId="27" headerRowBorderDxfId="26" tableBorderDxfId="25" totalsRowBorderDxfId="24">
   <autoFilter ref="B3:G47" xr:uid="{B787B3A6-2CEE-4580-AFD7-41F639EDECDD}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{939F0159-4F9B-4057-9BC5-36D344F3B8AC}" uniqueName="1" name="distance" queryTableFieldId="1" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{81B499A8-0D93-47F1-A1B2-353B11C7EBFD}" uniqueName="2" name="f1" queryTableFieldId="2" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{B7879AD2-073F-4B6B-808A-2A96D7E39690}" uniqueName="3" name="f2" queryTableFieldId="3" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{505BCF72-3549-4ECE-82AC-D43412A35DC6}" uniqueName="4" name="f3" queryTableFieldId="4" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{83B3B0AA-6769-459F-B298-721B2BBB03F9}" uniqueName="5" name="f4" queryTableFieldId="5" dataDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{0F80A3FC-7FBA-4E90-B532-78D8D4CD8CEF}" uniqueName="6" name="f5" queryTableFieldId="6" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{939F0159-4F9B-4057-9BC5-36D344F3B8AC}" uniqueName="1" name="distance" queryTableFieldId="1" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{81B499A8-0D93-47F1-A1B2-353B11C7EBFD}" uniqueName="2" name="f1" queryTableFieldId="2" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{B7879AD2-073F-4B6B-808A-2A96D7E39690}" uniqueName="3" name="f2" queryTableFieldId="3" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{505BCF72-3549-4ECE-82AC-D43412A35DC6}" uniqueName="4" name="f3" queryTableFieldId="4" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{83B3B0AA-6769-459F-B298-721B2BBB03F9}" uniqueName="5" name="f4" queryTableFieldId="5" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{0F80A3FC-7FBA-4E90-B532-78D8D4CD8CEF}" uniqueName="6" name="f5" queryTableFieldId="6" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{43EA538C-A70F-4D58-9DE1-930062C8AE1D}" name="PointsofCallinRacebyDistance" displayName="PointsofCallinRacebyDistance" ref="A2:F46" tableType="queryTable" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{43EA538C-A70F-4D58-9DE1-930062C8AE1D}" name="PointsofCallinRacebyDistance" displayName="PointsofCallinRacebyDistance" ref="A2:F46" tableType="queryTable" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="A2:F46" xr:uid="{43EA538C-A70F-4D58-9DE1-930062C8AE1D}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{05EEB0C5-140D-4ECF-9F88-0E72507177BD}" uniqueName="1" name="distance" queryTableFieldId="1" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{0AF1A642-5C49-4388-A378-E7AE01943968}" uniqueName="2" name="call1" queryTableFieldId="2" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{49C70756-8509-42F2-841B-35B2BA2D6A60}" uniqueName="3" name="call2" queryTableFieldId="3" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{CD322CDA-926E-40AB-958E-9FEDB5ACC064}" uniqueName="4" name="call3" queryTableFieldId="4" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{2812D68B-20B6-40A8-9828-3F4A71B3DBD8}" uniqueName="5" name="call4" queryTableFieldId="5" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{F7D0D449-A1AF-4E7B-92E5-A97D63897F85}" uniqueName="6" name="call5" queryTableFieldId="6" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{05EEB0C5-140D-4ECF-9F88-0E72507177BD}" uniqueName="1" name="distance" queryTableFieldId="1" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{0AF1A642-5C49-4388-A378-E7AE01943968}" uniqueName="2" name="call1" queryTableFieldId="2" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{49C70756-8509-42F2-841B-35B2BA2D6A60}" uniqueName="3" name="call2" queryTableFieldId="3" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{CD322CDA-926E-40AB-958E-9FEDB5ACC064}" uniqueName="4" name="call3" queryTableFieldId="4" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{2812D68B-20B6-40A8-9828-3F4A71B3DBD8}" uniqueName="5" name="call4" queryTableFieldId="5" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{F7D0D449-A1AF-4E7B-92E5-A97D63897F85}" uniqueName="6" name="call5" queryTableFieldId="6" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
